--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -456,7 +456,7 @@
         <v>5e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>0.900763</v>
+        <v>0.898195</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>4e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8700830000000001</v>
+        <v>0.891526</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -456,7 +456,7 @@
         <v>5e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>0.898195</v>
+        <v>0.899042</v>
       </c>
     </row>
     <row r="4">
@@ -469,7 +469,7 @@
         <v>4e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>0.891526</v>
+        <v>0.894541</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5e-06</v>
+        <v>0.051449</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5e-06</v>
+        <v>0.050796</v>
       </c>
       <c r="C3" t="n">
-        <v>0.899042</v>
+        <v>0.987312</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4e-06</v>
+        <v>0.044227</v>
       </c>
       <c r="C4" t="n">
-        <v>0.894541</v>
+        <v>0.8706739999999999</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.050796</v>
+        <v>0.050792</v>
       </c>
       <c r="C3" t="n">
-        <v>0.987312</v>
+        <v>0.987229</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.044227</v>
+        <v>0.04379</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8706739999999999</v>
+        <v>0.862137</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.050792</v>
+        <v>0.050769</v>
       </c>
       <c r="C3" t="n">
-        <v>0.987229</v>
+        <v>0.986772</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04379</v>
+        <v>0.04324</v>
       </c>
       <c r="C4" t="n">
-        <v>0.862137</v>
+        <v>0.8517</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.051449</v>
+        <v>0.012002</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.050769</v>
+        <v>0.011286</v>
       </c>
       <c r="C3" t="n">
-        <v>0.986772</v>
+        <v>0.940368</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04324</v>
+        <v>0.008696000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8517</v>
+        <v>0.77054</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.011286</v>
+        <v>0.011293</v>
       </c>
       <c r="C3" t="n">
-        <v>0.940368</v>
+        <v>0.940963</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008696000000000001</v>
+        <v>0.008798</v>
       </c>
       <c r="C4" t="n">
-        <v>0.77054</v>
+        <v>0.779084</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.012002</v>
+        <v>0.01417</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.011293</v>
+        <v>0.015334</v>
       </c>
       <c r="C3" t="n">
-        <v>0.940963</v>
+        <v>1.08215</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008798</v>
+        <v>0.012178</v>
       </c>
       <c r="C4" t="n">
-        <v>0.779084</v>
+        <v>0.79418</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015334</v>
+        <v>0.015327</v>
       </c>
       <c r="C3" t="n">
-        <v>1.08215</v>
+        <v>1.081622</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.012178</v>
+        <v>0.01231</v>
       </c>
       <c r="C4" t="n">
-        <v>0.79418</v>
+        <v>0.803185</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015327</v>
+        <v>0.015275</v>
       </c>
       <c r="C3" t="n">
-        <v>1.081622</v>
+        <v>1.077982</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01231</v>
+        <v>0.012771</v>
       </c>
       <c r="C4" t="n">
-        <v>0.803185</v>
+        <v>0.836086</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015275</v>
+        <v>0.015271</v>
       </c>
       <c r="C3" t="n">
-        <v>1.077982</v>
+        <v>1.077705</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.012771</v>
+        <v>0.012593</v>
       </c>
       <c r="C4" t="n">
-        <v>0.836086</v>
+        <v>0.824623</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015271</v>
+        <v>0.015167</v>
       </c>
       <c r="C3" t="n">
-        <v>1.077705</v>
+        <v>1.070366</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.012593</v>
+        <v>0.012643</v>
       </c>
       <c r="C4" t="n">
-        <v>0.824623</v>
+        <v>0.8336</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -456,7 +456,7 @@
         <v>0.015167</v>
       </c>
       <c r="C3" t="n">
-        <v>1.070366</v>
+        <v>1.070351</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.012643</v>
+        <v>0.012635</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8336</v>
+        <v>0.833032</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015167</v>
+        <v>0.015136</v>
       </c>
       <c r="C3" t="n">
-        <v>1.070351</v>
+        <v>1.068141</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.012635</v>
+        <v>0.012865</v>
       </c>
       <c r="C4" t="n">
-        <v>0.833032</v>
+        <v>0.849943</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015136</v>
+        <v>0.015141</v>
       </c>
       <c r="C3" t="n">
-        <v>1.068141</v>
+        <v>1.068535</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.012865</v>
+        <v>0.01287</v>
       </c>
       <c r="C4" t="n">
-        <v>0.849943</v>
+        <v>0.849996</v>
       </c>
     </row>
   </sheetData>

--- a/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
+++ b/vignettes/vignette-1/worked_example_mix_mismatch.xlsx
@@ -453,10 +453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.015141</v>
+        <v>0.015124</v>
       </c>
       <c r="C3" t="n">
-        <v>1.068535</v>
+        <v>1.067328</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01287</v>
+        <v>0.01275</v>
       </c>
       <c r="C4" t="n">
-        <v>0.849996</v>
+        <v>0.843008</v>
       </c>
     </row>
   </sheetData>
